--- a/04_試験/結合テスト/エビデンス.xlsx
+++ b/04_試験/結合テスト/エビデンス.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\システム開発演習\04_試験\結合テスト\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D59460D7-C27A-400F-B478-E08E74D0A982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54B2E4CD-117B-48AD-BEDC-B3DD46983535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61D45E01-00EF-4E4F-8C6E-8609400D9148}"/>
   </bookViews>
@@ -34,11 +34,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>項番</t>
     <rPh sb="0" eb="2">
       <t>コウバン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>再</t>
+    <rPh sb="0" eb="1">
+      <t>サイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -100,7 +107,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -111,6 +118,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -135,22 +145,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>126687</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>230850</xdr:rowOff>
+      <xdr:colOff>369075</xdr:colOff>
+      <xdr:row>175</xdr:row>
+      <xdr:rowOff>150000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>112726</xdr:colOff>
+      <xdr:row>194</xdr:row>
+      <xdr:rowOff>141105</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C23ED31-74F8-4CD3-93C9-AD80CA9979DC}"/>
+        <xdr:cNvPr id="97" name="図 96">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A665B1E-EFDB-4C5F-8A8E-3238C223883B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -172,8 +182,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1552575" y="3460437"/>
-          <a:ext cx="2181225" cy="2961663"/>
+          <a:off x="1502550" y="41821875"/>
+          <a:ext cx="5915851" cy="4515480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -187,25 +197,25 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>126687</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>295578</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>67065</xdr:rowOff>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>230850</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DB335FB-E8BA-40C1-A934-41DF7CF3B97F}"/>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C23ED31-74F8-4CD3-93C9-AD80CA9979DC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -215,6 +225,61 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1552575" y="3460437"/>
+          <a:ext cx="2181225" cy="2961663"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>295578</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>67065</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DB335FB-E8BA-40C1-A934-41DF7CF3B97F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -430,73 +495,18 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>161925</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>324255</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>124261</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="図 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FEA4DE6-8ADD-4681-BF7B-B2D2CFC22493}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1533525" y="7477125"/>
-          <a:ext cx="2905530" cy="3124636"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>565784</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>125730</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>194309</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>135255</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>360044</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>57151</xdr:rowOff>
+      <xdr:colOff>674369</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>66676</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -511,7 +521,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4442459" y="7745730"/>
+          <a:off x="4756784" y="14899005"/>
           <a:ext cx="2537460" cy="645796"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -592,15 +602,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>489585</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>209550</xdr:rowOff>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>470535</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -615,7 +625,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5943600" y="11963400"/>
+          <a:off x="6610350" y="19145250"/>
           <a:ext cx="2537460" cy="628650"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -693,1393 +703,18 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>257175</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>410171</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>9915</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55919D6D-8523-43E3-9E5F-9D85C98360C2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1390650" y="11982450"/>
-          <a:ext cx="4267796" cy="2791215"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>276225</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>457512</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>190880</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="図 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{83A5DD20-8A63-4E78-9715-F0E8607C2CD6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1409700" y="15087600"/>
-          <a:ext cx="2238687" cy="2724530"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>143238</xdr:colOff>
-      <xdr:row>92</xdr:row>
-      <xdr:rowOff>29002</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="図 15">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47EF34F1-E632-4253-969B-C05401AAF611}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1419225" y="18878550"/>
-          <a:ext cx="2600688" cy="3057952"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>292875</xdr:colOff>
+      <xdr:colOff>190500</xdr:colOff>
       <xdr:row>93</xdr:row>
-      <xdr:rowOff>130950</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>607531</xdr:colOff>
-      <xdr:row>105</xdr:row>
-      <xdr:rowOff>83717</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="図 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF55E400-5755-412F-81BB-DD0FE3F1ACB7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1426350" y="22276575"/>
-          <a:ext cx="2372056" cy="2810267"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>323850</xdr:colOff>
-      <xdr:row>109</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>476558</xdr:colOff>
-      <xdr:row>121</xdr:row>
-      <xdr:rowOff>9908</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="20" name="図 19">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D772129-94F8-487A-938B-6A05E78958E2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1457325" y="26079450"/>
-          <a:ext cx="2210108" cy="2743583"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>330975</xdr:colOff>
-      <xdr:row>122</xdr:row>
-      <xdr:rowOff>150000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>522172</xdr:colOff>
-      <xdr:row>128</xdr:row>
-      <xdr:rowOff>73989</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="22" name="図 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{836DBECD-4FE3-453E-AA02-00D9BBB9F046}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1464450" y="29201250"/>
-          <a:ext cx="4991797" cy="1352739"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>361950</xdr:colOff>
-      <xdr:row>132</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>638501</xdr:colOff>
-      <xdr:row>144</xdr:row>
-      <xdr:rowOff>133744</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="24" name="図 23">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{532E40C3-50EB-4950-BD75-58DD10D33EEC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1495425" y="31603950"/>
-          <a:ext cx="2333951" cy="2819794"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>359550</xdr:colOff>
-      <xdr:row>145</xdr:row>
-      <xdr:rowOff>226200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>64904</xdr:colOff>
-      <xdr:row>157</xdr:row>
-      <xdr:rowOff>159915</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="26" name="図 25">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{927D39DA-44D3-45A4-BFBB-8BAA9C79DFC7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1493025" y="34754325"/>
-          <a:ext cx="4505954" cy="2791215"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>352425</xdr:colOff>
-      <xdr:row>162</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>505133</xdr:colOff>
-      <xdr:row>174</xdr:row>
-      <xdr:rowOff>95642</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="28" name="図 27">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E51F6B5-9692-42F0-98B2-F2D16F60ABD1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1485900" y="38719125"/>
-          <a:ext cx="2210108" cy="2810267"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>340500</xdr:colOff>
-      <xdr:row>175</xdr:row>
-      <xdr:rowOff>169050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>531601</xdr:colOff>
-      <xdr:row>187</xdr:row>
-      <xdr:rowOff>74186</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="30" name="図 29">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24569741-202C-40F7-9C50-6422DEDF772D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1473975" y="41840925"/>
-          <a:ext cx="4305901" cy="2762636"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>361950</xdr:colOff>
-      <xdr:row>191</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>210486</xdr:colOff>
-      <xdr:row>201</xdr:row>
-      <xdr:rowOff>86044</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="32" name="図 31">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28F4B794-E7ED-4009-AFC8-70207D5B72DF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1495425" y="45662850"/>
-          <a:ext cx="6706536" cy="2286319"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>369075</xdr:colOff>
-      <xdr:row>202</xdr:row>
-      <xdr:rowOff>159525</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>227137</xdr:colOff>
-      <xdr:row>223</xdr:row>
-      <xdr:rowOff>26854</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="34" name="図 33">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{826549D3-F2B9-4B23-A1CA-9D25C8BF2BD0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1502550" y="48260775"/>
-          <a:ext cx="6716062" cy="4867954"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>227</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>191431</xdr:colOff>
-      <xdr:row>247</xdr:row>
-      <xdr:rowOff>229277</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="36" name="図 35">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93815329-1A54-489B-97E0-42D859C81DEC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1514475" y="54197250"/>
-          <a:ext cx="6668431" cy="4848902"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>388125</xdr:colOff>
-      <xdr:row>249</xdr:row>
-      <xdr:rowOff>64275</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>236661</xdr:colOff>
-      <xdr:row>258</xdr:row>
-      <xdr:rowOff>207469</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="38" name="図 37">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44642ADB-C694-4AF7-904B-4EBB96E8C69C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1521600" y="59357400"/>
-          <a:ext cx="6706536" cy="2286319"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>361950</xdr:colOff>
-      <xdr:row>263</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>267644</xdr:colOff>
-      <xdr:row>272</xdr:row>
-      <xdr:rowOff>209858</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="40" name="図 39">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0FB3191D-2072-4204-883E-D2380379E91B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1495425" y="62769750"/>
-          <a:ext cx="6763694" cy="2210108"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>359550</xdr:colOff>
-      <xdr:row>274</xdr:row>
-      <xdr:rowOff>45225</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>227139</xdr:colOff>
-      <xdr:row>294</xdr:row>
-      <xdr:rowOff>83995</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="42" name="図 41">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14E196C5-3425-4A75-AD95-80B5152E611D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1493025" y="65291475"/>
-          <a:ext cx="6725589" cy="4801270"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>371475</xdr:colOff>
-      <xdr:row>298</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>239064</xdr:colOff>
-      <xdr:row>318</xdr:row>
-      <xdr:rowOff>143545</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="44" name="図 43">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E883D6C7-5F7B-4171-BF04-A5A5721BE7F5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1504950" y="71066025"/>
-          <a:ext cx="6725589" cy="4801270"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>369075</xdr:colOff>
-      <xdr:row>319</xdr:row>
-      <xdr:rowOff>216675</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>160453</xdr:colOff>
-      <xdr:row>329</xdr:row>
-      <xdr:rowOff>16954</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="46" name="図 45">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7ED8AB38-BD2E-47FA-B2CB-D33AE0DF5D01}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1502550" y="76178550"/>
-          <a:ext cx="6649378" cy="2181529"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>371475</xdr:colOff>
-      <xdr:row>333</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>571815</xdr:colOff>
-      <xdr:row>345</xdr:row>
-      <xdr:rowOff>48013</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="48" name="図 47">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09E2D3E8-7124-48AD-A477-0F8C351E7C45}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1504950" y="79419450"/>
-          <a:ext cx="2257740" cy="2781688"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>359550</xdr:colOff>
-      <xdr:row>346</xdr:row>
-      <xdr:rowOff>111900</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>559890</xdr:colOff>
-      <xdr:row>359</xdr:row>
-      <xdr:rowOff>36121</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="図 49">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5508781A-40A4-4088-B6E3-44684EB55D27}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1493025" y="82503150"/>
-          <a:ext cx="2257740" cy="3019846"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>363</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>181713</xdr:colOff>
-      <xdr:row>372</xdr:row>
-      <xdr:rowOff>28857</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="52" name="図 51">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2D26979-48B8-40B9-AA4C-A43D46F2B456}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1514475" y="86591775"/>
-          <a:ext cx="5287113" cy="2019582"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>397650</xdr:colOff>
-      <xdr:row>373</xdr:row>
-      <xdr:rowOff>130950</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>64611</xdr:colOff>
-      <xdr:row>386</xdr:row>
-      <xdr:rowOff>17066</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="54" name="図 53">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4CFA9817-F802-4766-BD0A-4F989DB9BDAF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1531125" y="88951575"/>
-          <a:ext cx="2410161" cy="2981741"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>404775</xdr:colOff>
-      <xdr:row>387</xdr:row>
-      <xdr:rowOff>128550</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>128894</xdr:colOff>
-      <xdr:row>406</xdr:row>
-      <xdr:rowOff>81550</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="56" name="図 55">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E773A29-E234-43C4-86EF-EA6046D6DEDD}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1538250" y="92282925"/>
-          <a:ext cx="2467319" cy="4477375"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>390525</xdr:colOff>
-      <xdr:row>410</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>238869</xdr:colOff>
-      <xdr:row>418</xdr:row>
-      <xdr:rowOff>105041</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="58" name="図 57">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9635A4A-3F18-4B84-ACCE-08AB3399FB3B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1524000" y="97736025"/>
-          <a:ext cx="5334744" cy="1905266"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>397650</xdr:colOff>
-      <xdr:row>419</xdr:row>
-      <xdr:rowOff>178575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>255521</xdr:colOff>
-      <xdr:row>428</xdr:row>
-      <xdr:rowOff>216979</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="60" name="図 59">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8AFAC37-0203-4573-90C7-69D42422C9F0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1531125" y="99952950"/>
-          <a:ext cx="5344271" cy="2181529"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>565785</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:colOff>670560</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2094,7 +729,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3962400" y="15116175"/>
+          <a:off x="4067175" y="22269450"/>
           <a:ext cx="2537460" cy="628650"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2175,15 +810,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>175260</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>584835</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2198,7 +833,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4257675" y="18878550"/>
+          <a:off x="3981450" y="26060400"/>
           <a:ext cx="2537460" cy="628650"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2279,15 +914,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>93</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>123</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>661035</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:colOff>594360</xdr:colOff>
+      <xdr:row>125</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2302,7 +937,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4057650" y="22278975"/>
+          <a:off x="3990975" y="29337000"/>
           <a:ext cx="2537460" cy="628650"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2383,14 +1018,14 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>109</xdr:row>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>139</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>622935</xdr:colOff>
-      <xdr:row>112</xdr:row>
+      <xdr:colOff>641985</xdr:colOff>
+      <xdr:row>142</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2406,7 +1041,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4019550" y="26098500"/>
+          <a:off x="4038600" y="33242250"/>
           <a:ext cx="2537460" cy="628650"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2487,15 +1122,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>122</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>584835</xdr:colOff>
-      <xdr:row>125</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>152</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>99060</xdr:colOff>
+      <xdr:row>155</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2510,7 +1145,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6724650" y="29175075"/>
+          <a:off x="6924675" y="36309300"/>
           <a:ext cx="2537460" cy="628650"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2591,15 +1226,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>132</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>162</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>680085</xdr:colOff>
-      <xdr:row>135</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:colOff>594360</xdr:colOff>
+      <xdr:row>165</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2614,7 +1249,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4076700" y="31603950"/>
+          <a:off x="3990975" y="38681025"/>
           <a:ext cx="2537460" cy="628650"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2694,16 +1329,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>371475</xdr:colOff>
-      <xdr:row>145</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>165735</xdr:colOff>
-      <xdr:row>148</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>175</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>137160</xdr:colOff>
+      <xdr:row>178</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2718,7 +1353,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6305550" y="34747200"/>
+          <a:off x="7648575" y="41814750"/>
           <a:ext cx="2537460" cy="628650"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2800,13 +1435,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>161925</xdr:colOff>
-      <xdr:row>162</xdr:row>
+      <xdr:row>199</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>641985</xdr:colOff>
-      <xdr:row>165</xdr:row>
+      <xdr:row>202</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2902,16 +1537,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>175</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>613410</xdr:colOff>
-      <xdr:row>178</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>212</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>337185</xdr:colOff>
+      <xdr:row>214</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2926,7 +1561,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6067425" y="41833800"/>
+          <a:off x="7848600" y="48853725"/>
           <a:ext cx="2537460" cy="628650"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3006,16 +1641,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>514350</xdr:colOff>
-      <xdr:row>191</xdr:row>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>249</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>470535</xdr:colOff>
+      <xdr:row>251</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>308610</xdr:colOff>
-      <xdr:row>194</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3030,7 +1665,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8505825" y="45634275"/>
+          <a:off x="6610350" y="59293125"/>
           <a:ext cx="2537460" cy="628650"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3065,7 +1700,7 @@
         <a:p>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-            <a:t>1) </a:t>
+            <a:t>2) </a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
@@ -3110,16 +1745,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>561975</xdr:colOff>
-      <xdr:row>202</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>356235</xdr:colOff>
-      <xdr:row>205</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>259</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>99060</xdr:colOff>
+      <xdr:row>262</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3134,7 +1769,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8553450" y="48263175"/>
+          <a:off x="6924675" y="61769625"/>
           <a:ext cx="2537460" cy="628650"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3169,7 +1804,7 @@
         <a:p>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-            <a:t>2) </a:t>
+            <a:t>3) </a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
@@ -3214,16 +1849,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>227</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>299085</xdr:colOff>
-      <xdr:row>230</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>297</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>241935</xdr:colOff>
+      <xdr:row>299</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3238,7 +1873,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8496300" y="54178200"/>
+          <a:off x="7067550" y="70789800"/>
           <a:ext cx="2537460" cy="628650"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3273,7 +1908,7 @@
         <a:p>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-            <a:t>1) </a:t>
+            <a:t>2) </a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
@@ -3318,16 +1953,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>514350</xdr:colOff>
-      <xdr:row>249</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>308610</xdr:colOff>
-      <xdr:row>251</xdr:row>
-      <xdr:rowOff>209550</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>318</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>499110</xdr:colOff>
+      <xdr:row>321</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3342,7 +1977,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8505825" y="59350275"/>
+          <a:off x="6638925" y="75838050"/>
           <a:ext cx="2537460" cy="628650"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3377,7 +2012,7 @@
         <a:p>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-            <a:t>2) </a:t>
+            <a:t>3) </a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
@@ -3422,16 +2057,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>600075</xdr:colOff>
-      <xdr:row>263</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>394335</xdr:colOff>
-      <xdr:row>266</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>345</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>556260</xdr:colOff>
+      <xdr:row>348</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3446,7 +2081,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8591550" y="62760225"/>
+          <a:off x="6696075" y="82238850"/>
           <a:ext cx="2537460" cy="628650"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3481,7 +2116,7 @@
         <a:p>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-            <a:t>1) </a:t>
+            <a:t>2) </a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
@@ -3526,16 +2161,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>590550</xdr:colOff>
-      <xdr:row>274</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>384810</xdr:colOff>
-      <xdr:row>276</xdr:row>
-      <xdr:rowOff>209550</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>355</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>146685</xdr:colOff>
+      <xdr:row>358</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3550,7 +2185,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8582025" y="65303400"/>
+          <a:off x="6972300" y="84667725"/>
           <a:ext cx="2537460" cy="628650"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3585,7 +2220,7 @@
         <a:p>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-            <a:t>2) </a:t>
+            <a:t>3) </a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
@@ -3630,16 +2265,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>590550</xdr:colOff>
-      <xdr:row>298</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>384810</xdr:colOff>
-      <xdr:row>301</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>393</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>395</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3654,7 +2289,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8582025" y="71056500"/>
+          <a:off x="7000875" y="93659325"/>
           <a:ext cx="2537460" cy="628650"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3689,7 +2324,7 @@
         <a:p>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-            <a:t>1) </a:t>
+            <a:t>2) </a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
@@ -3734,16 +2369,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>466725</xdr:colOff>
-      <xdr:row>319</xdr:row>
-      <xdr:rowOff>209550</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>260985</xdr:colOff>
-      <xdr:row>322</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>414</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>546735</xdr:colOff>
+      <xdr:row>417</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3758,7 +2393,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8458200" y="76171425"/>
+          <a:off x="6686550" y="98717100"/>
           <a:ext cx="2537460" cy="628650"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3793,7 +2428,7 @@
         <a:p>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-            <a:t>2) </a:t>
+            <a:t>3) </a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
@@ -3839,15 +2474,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>333</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>428</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>670560</xdr:colOff>
-      <xdr:row>336</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:colOff>575310</xdr:colOff>
+      <xdr:row>431</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3862,7 +2497,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4067175" y="79438500"/>
+          <a:off x="3971925" y="102050850"/>
           <a:ext cx="2537460" cy="628650"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3943,15 +2578,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>346</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>32385</xdr:colOff>
-      <xdr:row>349</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>441</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>594360</xdr:colOff>
+      <xdr:row>443</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3966,7 +2601,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4114800" y="82505550"/>
+          <a:off x="3990975" y="105070275"/>
           <a:ext cx="2537460" cy="628650"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4047,15 +2682,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>485775</xdr:colOff>
-      <xdr:row>363</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>280035</xdr:colOff>
-      <xdr:row>366</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>458</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>537210</xdr:colOff>
+      <xdr:row>461</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4070,7 +2705,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7105650" y="86572725"/>
+          <a:off x="6677025" y="109175550"/>
           <a:ext cx="2537460" cy="628650"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4151,15 +2786,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>409575</xdr:colOff>
-      <xdr:row>373</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>471</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>203835</xdr:colOff>
-      <xdr:row>376</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:colOff>13335</xdr:colOff>
+      <xdr:row>473</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4174,7 +2809,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4286250" y="88944450"/>
+          <a:off x="4095750" y="112233075"/>
           <a:ext cx="2537460" cy="628650"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4255,15 +2890,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>428625</xdr:colOff>
-      <xdr:row>387</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>484</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>222885</xdr:colOff>
-      <xdr:row>390</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:colOff>13335</xdr:colOff>
+      <xdr:row>487</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4278,7 +2913,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4305300" y="92268675"/>
+          <a:off x="4095750" y="115433475"/>
           <a:ext cx="2537460" cy="628650"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4359,15 +2994,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>523875</xdr:colOff>
-      <xdr:row>410</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>318135</xdr:colOff>
-      <xdr:row>413</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>504</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>546735</xdr:colOff>
+      <xdr:row>507</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4382,7 +3017,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7143750" y="97755075"/>
+          <a:off x="6686550" y="120119775"/>
           <a:ext cx="2537460" cy="628650"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4463,15 +3098,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>419</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>337185</xdr:colOff>
-      <xdr:row>422</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>517</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>622935</xdr:colOff>
+      <xdr:row>519</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4486,7 +3121,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7162800" y="99955350"/>
+          <a:off x="6762750" y="123177300"/>
           <a:ext cx="2537460" cy="628650"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4566,16 +3201,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>152</xdr:row>
-      <xdr:rowOff>76199</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>156</xdr:row>
-      <xdr:rowOff>123824</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>189</xdr:row>
+      <xdr:rowOff>95249</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>193</xdr:row>
+      <xdr:rowOff>142874</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4590,7 +3225,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6391275" y="36271199"/>
+          <a:off x="7677150" y="45100874"/>
           <a:ext cx="2524125" cy="1000125"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4644,15 +3279,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>154</xdr:row>
-      <xdr:rowOff>100012</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>154</xdr:row>
-      <xdr:rowOff>114301</xdr:rowOff>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>191</xdr:row>
+      <xdr:rowOff>104776</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>191</xdr:row>
+      <xdr:rowOff>119062</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -4669,9 +3304,9 @@
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="2533650" y="36771262"/>
-          <a:ext cx="3857625" cy="14289"/>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="2562225" y="45586651"/>
+          <a:ext cx="5114925" cy="14286"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -4703,15 +3338,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>154</xdr:row>
-      <xdr:rowOff>28576</xdr:rowOff>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>191</xdr:row>
+      <xdr:rowOff>19051</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>154</xdr:row>
-      <xdr:rowOff>200025</xdr:rowOff>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>191</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4726,7 +3361,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1514475" y="36699826"/>
+          <a:off x="1543050" y="45500926"/>
           <a:ext cx="1019175" cy="171449"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4764,6 +3399,2979 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>632460</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>59055</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="76" name="テキスト ボックス 75">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54A6CD44-806B-44EA-8A6B-E48D6421C834}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3952875" y="7764780"/>
+          <a:ext cx="1927860" cy="628650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>1.1) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>商品検索</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>画面</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>※</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>初期表示</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>609599</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>504824</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="77" name="テキスト ボックス 76">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74CDC2AC-5500-489D-8970-9E54374D44DD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3800474" y="10877550"/>
+          <a:ext cx="1952625" cy="628650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>1.2) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>商品検索画面</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>※</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>初期表示</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{622159B2-5E7E-4F76-B089-950C8E92439D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1333500" y="1323975"/>
+          <a:ext cx="1743075" cy="276225"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>638175</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="78" name="正方形/長方形 77">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1C288D1-B900-4546-BCC7-EC6DC123C912}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1314450" y="4476750"/>
+          <a:ext cx="1828800" cy="276225"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>230505</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="79" name="テキスト ボックス 78">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB53D2E6-6EF5-4A6C-B4D1-E470BA72ACE7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4038600" y="1421130"/>
+          <a:ext cx="2076450" cy="579120"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>・存在しないはずのプレースホルダーが表示されている。</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>190499</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>211455</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>200024</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="80" name="テキスト ボックス 79">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{633477F3-274E-4A26-8217-7CE455EC7C73}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4067174" y="4497705"/>
+          <a:ext cx="2066925" cy="617220"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>・存在しないはずのプレースホルダーが表示されている。</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>33338</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>43815</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="13" name="直線矢印コネクタ 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{817BC6CF-E9D3-4A51-ACD1-F4EDE1235A85}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="79" idx="1"/>
+          <a:endCxn id="2" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="3076575" y="1462088"/>
+          <a:ext cx="962025" cy="248602"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>638175</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>90488</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>190499</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>43815</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="81" name="直線矢印コネクタ 80">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B3224E5-81B5-41C6-AF97-0E792B8D3A1E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="80" idx="1"/>
+          <a:endCxn id="78" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="3143250" y="4614863"/>
+          <a:ext cx="923924" cy="191452"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>543240</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>143274</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="27" name="図 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D838574-EB78-4081-8FEF-53E5DBDCEE5B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1476375" y="7762875"/>
+          <a:ext cx="2257740" cy="2857899"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>340500</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>178575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>426524</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>36079</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="31" name="図 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F827717B-441A-407A-BDF9-22CF5288979A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1473975" y="10894200"/>
+          <a:ext cx="2143424" cy="2715004"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>600488</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>67098</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="35" name="図 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67890381-2FC4-41BF-901B-351ECBFFD62E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1514475" y="14897100"/>
+          <a:ext cx="2962688" cy="3029373"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>486456</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>200405</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="83" name="図 82">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{964DBC33-65E6-4FCD-B0A7-73EC7451233E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1543050" y="19145250"/>
+          <a:ext cx="4877481" cy="2724530"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>407175</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>130950</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>636094</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>198000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="85" name="図 84">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{589921F7-2A5E-4920-A4E0-998AF93496DB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1540650" y="22276575"/>
+          <a:ext cx="2286319" cy="2686425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>524183</xdr:colOff>
+      <xdr:row>121</xdr:row>
+      <xdr:rowOff>162332</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="87" name="図 86">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2C0BF2F-4741-460C-BBEF-F37D108AF7B1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1504950" y="26060400"/>
+          <a:ext cx="2210108" cy="2915057"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>359550</xdr:colOff>
+      <xdr:row>123</xdr:row>
+      <xdr:rowOff>45225</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>550364</xdr:colOff>
+      <xdr:row>134</xdr:row>
+      <xdr:rowOff>159907</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="89" name="図 88">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25C08D78-4660-4357-9451-90D9EB341B06}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1493025" y="29334600"/>
+          <a:ext cx="2248214" cy="2734057"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>199</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>638485</xdr:colOff>
+      <xdr:row>211</xdr:row>
+      <xdr:rowOff>38483</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="91" name="図 90">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC296E01-FC31-4A79-83AF-C7E4ECD631D2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1609725" y="45872400"/>
+          <a:ext cx="2219635" cy="2743583"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>464325</xdr:colOff>
+      <xdr:row>212</xdr:row>
+      <xdr:rowOff>45225</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>246081</xdr:colOff>
+      <xdr:row>232</xdr:row>
+      <xdr:rowOff>26837</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="93" name="図 92">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F96A7C1A-2BA2-4003-955A-B2CFC9C683CE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1597800" y="48860850"/>
+          <a:ext cx="5953956" cy="4744112"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>162</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>581340</xdr:colOff>
+      <xdr:row>174</xdr:row>
+      <xdr:rowOff>38487</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="95" name="図 94">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49112245-0A92-463A-8065-02434FBB6695}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1514475" y="38700075"/>
+          <a:ext cx="2257740" cy="2772162"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>571814</xdr:colOff>
+      <xdr:row>150</xdr:row>
+      <xdr:rowOff>200400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="101" name="図 100">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B4B080CC-14B5-4B45-B43D-6BE68492F64E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1514475" y="33232725"/>
+          <a:ext cx="2248214" cy="2686425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>378600</xdr:colOff>
+      <xdr:row>152</xdr:row>
+      <xdr:rowOff>121425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>646007</xdr:colOff>
+      <xdr:row>158</xdr:row>
+      <xdr:rowOff>83519</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="103" name="図 102">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6D0A110-8774-4E3C-A0EF-0D3731883BA9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1512075" y="36316425"/>
+          <a:ext cx="5068007" cy="1390844"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>191</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>308610</xdr:colOff>
+      <xdr:row>194</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="104" name="テキスト ボックス 103">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE5368DF-F1F0-41C3-AC69-AE1DB4E63E53}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8505825" y="45634275"/>
+          <a:ext cx="2537460" cy="628650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>1) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>商品検索結果</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>画面</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>※</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>遷移前</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>236</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>3810</xdr:colOff>
+      <xdr:row>239</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="105" name="テキスト ボックス 104">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19C84D47-DD39-49BE-B7E0-FB8AE44C4389}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4086225" y="56321325"/>
+          <a:ext cx="2537460" cy="800100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>1) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>商品検索</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>画面</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>※</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>入力した検索キーワードと、選択した商品カテゴリー</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>236</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>600399</xdr:colOff>
+      <xdr:row>248</xdr:row>
+      <xdr:rowOff>9909</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="107" name="図 106">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05D29AE2-4735-4D8B-A2D2-4B61B7608E31}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1466850" y="56311800"/>
+          <a:ext cx="2324424" cy="2753109"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>330975</xdr:colOff>
+      <xdr:row>249</xdr:row>
+      <xdr:rowOff>16650</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>436435</xdr:colOff>
+      <xdr:row>258</xdr:row>
+      <xdr:rowOff>36002</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="109" name="図 108">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E3820E9-4540-4C57-8A71-AE365D3F5287}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1464450" y="59309775"/>
+          <a:ext cx="4906060" cy="2162477"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>347625</xdr:colOff>
+      <xdr:row>259</xdr:row>
+      <xdr:rowOff>99975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>43548</xdr:colOff>
+      <xdr:row>279</xdr:row>
+      <xdr:rowOff>110166</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="111" name="図 110">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48194A6A-D3EA-4B7C-A420-14E7157AB487}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1481100" y="61774350"/>
+          <a:ext cx="5182323" cy="4772691"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>284</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>680085</xdr:colOff>
+      <xdr:row>287</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="112" name="テキスト ボックス 111">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1A9FEC9-2232-4B3F-BDCD-713FF81E0B88}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4076700" y="67722750"/>
+          <a:ext cx="2537460" cy="800100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>1) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>商品検索</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>画面</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>※</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>入力した検索キーワードと、選択した商品カテゴリー</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>284</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>590874</xdr:colOff>
+      <xdr:row>296</xdr:row>
+      <xdr:rowOff>384</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="114" name="図 113">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{252E8278-9098-455A-BFD3-3D31DB3B32D1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1457325" y="67732275"/>
+          <a:ext cx="2324424" cy="2753109"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>330975</xdr:colOff>
+      <xdr:row>297</xdr:row>
+      <xdr:rowOff>64275</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>179319</xdr:colOff>
+      <xdr:row>317</xdr:row>
+      <xdr:rowOff>103045</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="116" name="図 115">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F19A13F-3D35-4136-AF77-0C983F058F03}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1464450" y="70787400"/>
+          <a:ext cx="5334744" cy="4801270"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>328575</xdr:colOff>
+      <xdr:row>318</xdr:row>
+      <xdr:rowOff>128550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>434035</xdr:colOff>
+      <xdr:row>327</xdr:row>
+      <xdr:rowOff>147902</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="118" name="図 117">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{887D8874-4452-4D3D-9638-86E122E0809D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1462050" y="75852300"/>
+          <a:ext cx="4906060" cy="2162477"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>332</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>632460</xdr:colOff>
+      <xdr:row>335</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="119" name="テキスト ボックス 118">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66870EF0-9FD6-4DFB-BB66-2D07BC1E18C8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4029075" y="79181325"/>
+          <a:ext cx="2537460" cy="800100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>1) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>商品検索</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>画面</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>※</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>入力した検索キーワードと、選択した商品カテゴリー</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>332</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>571814</xdr:colOff>
+      <xdr:row>344</xdr:row>
+      <xdr:rowOff>28959</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="121" name="図 120">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1DAB82E8-0F73-476F-9356-F7D5CA233F76}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1514475" y="79190850"/>
+          <a:ext cx="2248214" cy="2753109"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>369075</xdr:colOff>
+      <xdr:row>345</xdr:row>
+      <xdr:rowOff>83325</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>503114</xdr:colOff>
+      <xdr:row>354</xdr:row>
+      <xdr:rowOff>55045</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="123" name="図 122">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{916D9420-3F3D-4093-9EF7-110729ADFED8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1502550" y="82236450"/>
+          <a:ext cx="4934639" cy="2114845"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>385725</xdr:colOff>
+      <xdr:row>355</xdr:row>
+      <xdr:rowOff>147600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>81648</xdr:colOff>
+      <xdr:row>375</xdr:row>
+      <xdr:rowOff>62528</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="125" name="図 124">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20F6843D-F670-4288-B82F-83AD77758602}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1519200" y="84681975"/>
+          <a:ext cx="5182323" cy="4677428"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>380</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>594360</xdr:colOff>
+      <xdr:row>383</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="126" name="テキスト ボックス 125">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FAAF756A-8BB4-4AE8-B2FD-15A9390E1946}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3990975" y="90611325"/>
+          <a:ext cx="2537460" cy="800100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>1) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>商品検索</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>画面</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>※</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>入力した検索キーワードと、選択した商品カテゴリー</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>380</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>543239</xdr:colOff>
+      <xdr:row>392</xdr:row>
+      <xdr:rowOff>19434</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="128" name="図 127">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F06417AB-9C3B-4A81-82CA-C6E8DE74F8C4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1485900" y="90611325"/>
+          <a:ext cx="2248214" cy="2753109"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>350025</xdr:colOff>
+      <xdr:row>393</xdr:row>
+      <xdr:rowOff>64275</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>131685</xdr:colOff>
+      <xdr:row>413</xdr:row>
+      <xdr:rowOff>83992</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="130" name="図 129">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B0A65940-6B2B-4F7E-B739-AAD4E34AA207}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1483500" y="93647400"/>
+          <a:ext cx="5268060" cy="4782217"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>366675</xdr:colOff>
+      <xdr:row>414</xdr:row>
+      <xdr:rowOff>147600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>500714</xdr:colOff>
+      <xdr:row>423</xdr:row>
+      <xdr:rowOff>119320</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="132" name="図 131">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A88320F7-6DEB-48F3-82E5-A7C56EB0FB48}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1500150" y="98731350"/>
+          <a:ext cx="4934639" cy="2114845"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>428</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>562287</xdr:colOff>
+      <xdr:row>439</xdr:row>
+      <xdr:rowOff>209928</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="134" name="図 133">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD8F6F9D-AFFA-4028-99A8-3AC22045D421}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1514475" y="102041325"/>
+          <a:ext cx="2238687" cy="2705478"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>369075</xdr:colOff>
+      <xdr:row>441</xdr:row>
+      <xdr:rowOff>54750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>550362</xdr:colOff>
+      <xdr:row>453</xdr:row>
+      <xdr:rowOff>159938</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="136" name="図 135">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A963084-AE9E-48FC-8893-4430E4B3D5D1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1502550" y="105067875"/>
+          <a:ext cx="2238687" cy="2962688"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>458</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>495991</xdr:colOff>
+      <xdr:row>469</xdr:row>
+      <xdr:rowOff>219455</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="148" name="図 147">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{713D2D4B-A91C-4630-89A9-67F9C6EB48B4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1476375" y="109175550"/>
+          <a:ext cx="4953691" cy="2724530"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>340500</xdr:colOff>
+      <xdr:row>471</xdr:row>
+      <xdr:rowOff>73800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>617051</xdr:colOff>
+      <xdr:row>483</xdr:row>
+      <xdr:rowOff>140883</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="150" name="図 149">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70B1E75C-CC6F-458C-936D-0CB7C6A3D4AE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1473975" y="112230675"/>
+          <a:ext cx="2333951" cy="2924583"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>338100</xdr:colOff>
+      <xdr:row>484</xdr:row>
+      <xdr:rowOff>185700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>633703</xdr:colOff>
+      <xdr:row>499</xdr:row>
+      <xdr:rowOff>81409</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="152" name="図 151">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61B22EC7-0A5A-49FC-92ED-7D563917D508}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1471575" y="115438200"/>
+          <a:ext cx="2353003" cy="3467584"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>504</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>515040</xdr:colOff>
+      <xdr:row>516</xdr:row>
+      <xdr:rowOff>383</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="154" name="図 153">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10E1D6E8-45DA-4AFC-BB70-BAE0BADBB3BF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId29">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1504950" y="120129300"/>
+          <a:ext cx="4944165" cy="2743583"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>369075</xdr:colOff>
+      <xdr:row>517</xdr:row>
+      <xdr:rowOff>64275</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>541219</xdr:colOff>
+      <xdr:row>529</xdr:row>
+      <xdr:rowOff>198042</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="156" name="図 155">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DC87A99-A5EE-4164-980F-135B9846C436}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId30">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1502550" y="123174900"/>
+          <a:ext cx="4972744" cy="2991267"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -5066,7 +6674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BFE11A7-13B3-4FB3-89F0-5C00EF2C18C0}">
-  <dimension ref="B2:B411"/>
+  <dimension ref="B2:B505"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="5.875" customWidth="1"/>
@@ -5083,72 +6691,82 @@
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B33" s="1">
+      <c r="B33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B34" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B63" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B51" s="1">
+    <row r="81" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B81" s="1">
         <v>5</v>
-      </c>
-    </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B80">
-        <v>6</v>
       </c>
     </row>
     <row r="110" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B110">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="140" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B140">
         <v>7</v>
       </c>
     </row>
-    <row r="133" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B133">
+    <row r="163" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B163">
         <v>8</v>
       </c>
     </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B163" s="2">
+    <row r="200" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B200" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B164" s="3" t="s">
+    <row r="201" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B201" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B192">
+    <row r="237" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B237">
         <v>9</v>
       </c>
     </row>
-    <row r="228" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B228">
+    <row r="285" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B285">
         <v>10</v>
       </c>
     </row>
-    <row r="264" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B264">
+    <row r="333" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B333">
         <v>11</v>
       </c>
     </row>
-    <row r="299" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B299">
+    <row r="381" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B381">
         <v>12</v>
       </c>
     </row>
-    <row r="334" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B334">
+    <row r="429" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B429">
         <v>13</v>
       </c>
     </row>
-    <row r="364" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B364">
+    <row r="459" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B459">
         <v>14</v>
       </c>
     </row>
-    <row r="411" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B411">
+    <row r="505" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B505">
         <v>15</v>
       </c>
     </row>
